--- a/feedback_forms/026_organizational_awareness_survey--feedback_forms.xlsx
+++ b/feedback_forms/026_organizational_awareness_survey--feedback_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,11 +427,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -556,18 +556,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>objective_statement_2</t>
+          <t>feedback_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>What are our company's core values and objectives?</t>
+          <t>Can you elaborate on how you've seen these values and objectives reflected in your work?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -579,18 +579,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>objective_statement_3</t>
+          <t>feedback_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What are our company's core values and objectives?</t>
+          <t>How do you think these values and objectives impact your role and responsibilities?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -602,18 +602,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>objective_statement_4</t>
+          <t>feedback_3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>What are our company's core values and objectives?</t>
+          <t>Are there any areas where you think we could improve on these values and objectives?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -625,18 +625,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>objective_statement_5</t>
+          <t>feedback_4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>What are our company's core values and objectives?</t>
+          <t>How do you think these values and objectives align with your personal values and goals?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -648,18 +648,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>objective_statement_6</t>
+          <t>feedback_5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>What are our company's core values and objectives?</t>
+          <t>What is the biggest challenge you face in achieving these values and objectives?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -671,18 +671,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>objective_statement_7</t>
+          <t>feedback_6</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What are our company's core values and objectives?</t>
+          <t>How do you think we can overcome this challenge?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -694,18 +694,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>objective_statement_8</t>
+          <t>feedback_7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>What are our company's core values and objectives?</t>
+          <t>What resources do you think we need to provide to support you in achieving these values and objectives?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -717,18 +717,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>objective_statement_9</t>
+          <t>feedback_8</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>What are our company's core values and objectives?</t>
+          <t>Can you think of any ways we can recognize and reward employees for demonstrating these values and objectives?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -740,18 +740,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>objective_statement_10</t>
+          <t>feedback_9</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>What are our company's core values and objectives?</t>
+          <t>Are there any potential unintended consequences of adopting these values and objectives?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -763,18 +763,18 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>objective_statement_11</t>
+          <t>feedback_10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>What are our company's core values and objectives?</t>
+          <t>How do you think we can measure progress towards achieving these values and objectives?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -786,18 +786,18 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>objective_statement_12</t>
+          <t>vision_statement</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>What are our company's core values and objectives?</t>
+          <t>What are your thoughts on our company's vision statement?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -809,18 +809,18 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>objective_statement_13</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>What are our company's core values and objectives?</t>
+          <t>How do you think we can communicate effectively with employees about these values and objectives?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -832,18 +832,18 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>objective_statement_14</t>
+          <t>diversity</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>What are our company's core values and objectives?</t>
+          <t>Are there any cultural or diversity-related aspects of the company that you think are essential to achieving these values and objectives?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -855,18 +855,18 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>objective_statement_15</t>
+          <t>training</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>What are our company's core values and objectives?</t>
+          <t>Can you suggest any specific training or development opportunities that would support employees in achieving these values and objectives?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -878,18 +878,18 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>objective_statement_16</t>
+          <t>culture</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>What are our company's core values and objectives?</t>
+          <t>How do you think we can foster a culture of open communication about these values and objectives?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -901,294 +901,18 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>objective_statement_17</t>
+          <t>challenges</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>What are our company's core values and objectives?</t>
+          <t>Are there any potential barriers or obstacles to achieving these values and objectives?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>objective_statement_18</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>What are our company's core values and objectives?</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>objective_statement_19</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>What are our company's core values and objectives?</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>objective_statement_20</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>What are our company's core values and objectives?</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>objective_statement_21</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>What are our company's core values and objectives?</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>objective_statement_22</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>What are our company's core values and objectives?</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>objective_statement_23</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>What are our company's core values and objectives?</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>objective_statement_24</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>What are our company's core values and objectives?</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>objective_statement_25</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>What are our company's core values and objectives?</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>objective_statement_26</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>What are our company's core values and objectives?</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>objective_statement_27</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>What are our company's core values and objectives?</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>objective_statement_28</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>What are our company's core values and objectives?</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>objective_statement_29</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>What are our company's core values and objectives?</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
